--- a/進捗管理表_志賀.xlsx
+++ b/進捗管理表_志賀.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-04\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-04\Documents\project\MyTaskSystem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582C8596-5BE4-4D53-B34A-C49648D6736F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F4C107-F8A6-4D7E-A0CD-91E4BDA4FD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="42">
   <si>
     <t>■進捗管理表</t>
   </si>
@@ -1552,47 +1552,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1630,8 +1612,26 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1942,142 +1942,142 @@
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="98" t="s">
+      <c r="B3" s="114" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="109">
+      <c r="G3" s="103">
         <v>45705</v>
       </c>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="110"/>
-      <c r="M3" s="110"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="110"/>
-      <c r="P3" s="110"/>
-      <c r="Q3" s="110"/>
-      <c r="R3" s="110"/>
-      <c r="S3" s="110"/>
-      <c r="T3" s="110"/>
-      <c r="U3" s="110"/>
-      <c r="V3" s="110"/>
-      <c r="W3" s="110"/>
-      <c r="X3" s="110"/>
-      <c r="Y3" s="110"/>
-      <c r="Z3" s="110"/>
-      <c r="AA3" s="110"/>
-      <c r="AB3" s="110"/>
-      <c r="AC3" s="110"/>
-      <c r="AD3" s="110"/>
-      <c r="AE3" s="110"/>
-      <c r="AF3" s="110"/>
-      <c r="AG3" s="110"/>
-      <c r="AH3" s="110"/>
-      <c r="AI3" s="110"/>
-      <c r="AJ3" s="110"/>
-      <c r="AK3" s="110"/>
-      <c r="AL3" s="111"/>
+      <c r="H3" s="104"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="104"/>
+      <c r="K3" s="104"/>
+      <c r="L3" s="104"/>
+      <c r="M3" s="104"/>
+      <c r="N3" s="104"/>
+      <c r="O3" s="104"/>
+      <c r="P3" s="104"/>
+      <c r="Q3" s="104"/>
+      <c r="R3" s="104"/>
+      <c r="S3" s="104"/>
+      <c r="T3" s="104"/>
+      <c r="U3" s="104"/>
+      <c r="V3" s="104"/>
+      <c r="W3" s="104"/>
+      <c r="X3" s="104"/>
+      <c r="Y3" s="104"/>
+      <c r="Z3" s="104"/>
+      <c r="AA3" s="104"/>
+      <c r="AB3" s="104"/>
+      <c r="AC3" s="104"/>
+      <c r="AD3" s="104"/>
+      <c r="AE3" s="104"/>
+      <c r="AF3" s="104"/>
+      <c r="AG3" s="104"/>
+      <c r="AH3" s="104"/>
+      <c r="AI3" s="104"/>
+      <c r="AJ3" s="104"/>
+      <c r="AK3" s="104"/>
+      <c r="AL3" s="105"/>
     </row>
     <row r="4" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A4" s="97"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="99" t="s">
+      <c r="A4" s="113"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="115" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="96" t="s">
+      <c r="D4" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="103" t="s">
+      <c r="E4" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="106" t="s">
+      <c r="F4" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="112"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="113"/>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113"/>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113"/>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113"/>
-      <c r="V4" s="113"/>
-      <c r="W4" s="113"/>
-      <c r="X4" s="113"/>
-      <c r="Y4" s="113"/>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="113"/>
-      <c r="AE4" s="113"/>
-      <c r="AF4" s="113"/>
-      <c r="AG4" s="113"/>
-      <c r="AH4" s="113"/>
-      <c r="AI4" s="113"/>
-      <c r="AJ4" s="113"/>
-      <c r="AK4" s="113"/>
-      <c r="AL4" s="114"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="107"/>
+      <c r="L4" s="107"/>
+      <c r="M4" s="107"/>
+      <c r="N4" s="107"/>
+      <c r="O4" s="107"/>
+      <c r="P4" s="107"/>
+      <c r="Q4" s="107"/>
+      <c r="R4" s="107"/>
+      <c r="S4" s="107"/>
+      <c r="T4" s="107"/>
+      <c r="U4" s="107"/>
+      <c r="V4" s="107"/>
+      <c r="W4" s="107"/>
+      <c r="X4" s="107"/>
+      <c r="Y4" s="107"/>
+      <c r="Z4" s="107"/>
+      <c r="AA4" s="107"/>
+      <c r="AB4" s="107"/>
+      <c r="AC4" s="107"/>
+      <c r="AD4" s="107"/>
+      <c r="AE4" s="107"/>
+      <c r="AF4" s="107"/>
+      <c r="AG4" s="107"/>
+      <c r="AH4" s="107"/>
+      <c r="AI4" s="107"/>
+      <c r="AJ4" s="107"/>
+      <c r="AK4" s="107"/>
+      <c r="AL4" s="108"/>
     </row>
     <row r="5" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A5" s="97"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="104">
+      <c r="A5" s="113"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="97">
         <v>17</v>
       </c>
-      <c r="H5" s="105"/>
-      <c r="I5" s="100">
+      <c r="H5" s="98"/>
+      <c r="I5" s="99">
         <v>18</v>
       </c>
-      <c r="J5" s="101"/>
-      <c r="K5" s="100">
+      <c r="J5" s="116"/>
+      <c r="K5" s="99">
         <v>19</v>
       </c>
-      <c r="L5" s="101"/>
-      <c r="M5" s="100">
+      <c r="L5" s="116"/>
+      <c r="M5" s="99">
         <v>20</v>
       </c>
-      <c r="N5" s="101"/>
-      <c r="O5" s="100">
+      <c r="N5" s="116"/>
+      <c r="O5" s="99">
         <v>21</v>
       </c>
-      <c r="P5" s="101"/>
-      <c r="Q5" s="100">
+      <c r="P5" s="116"/>
+      <c r="Q5" s="99">
         <v>25</v>
       </c>
-      <c r="R5" s="102"/>
-      <c r="S5" s="104">
+      <c r="R5" s="117"/>
+      <c r="S5" s="97">
         <v>26</v>
       </c>
-      <c r="T5" s="105"/>
-      <c r="U5" s="100">
+      <c r="T5" s="98"/>
+      <c r="U5" s="99">
         <v>27</v>
       </c>
-      <c r="V5" s="105"/>
-      <c r="W5" s="100">
+      <c r="V5" s="98"/>
+      <c r="W5" s="99">
         <v>28</v>
       </c>
-      <c r="X5" s="105"/>
+      <c r="X5" s="98"/>
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
@@ -2094,48 +2094,48 @@
       <c r="AL5" s="11"/>
     </row>
     <row r="6" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A6" s="93"/>
-      <c r="B6" s="93"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="104" t="s">
+      <c r="A6" s="94"/>
+      <c r="B6" s="94"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="94"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="105"/>
-      <c r="I6" s="115" t="s">
+      <c r="H6" s="98"/>
+      <c r="I6" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="105"/>
-      <c r="K6" s="100" t="s">
+      <c r="J6" s="98"/>
+      <c r="K6" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="105"/>
-      <c r="M6" s="100" t="s">
+      <c r="L6" s="98"/>
+      <c r="M6" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="105"/>
-      <c r="O6" s="100" t="s">
+      <c r="N6" s="98"/>
+      <c r="O6" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="105"/>
-      <c r="Q6" s="100" t="s">
+      <c r="P6" s="98"/>
+      <c r="Q6" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="105"/>
-      <c r="S6" s="116" t="s">
+      <c r="R6" s="98"/>
+      <c r="S6" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="T6" s="105"/>
-      <c r="U6" s="117" t="s">
+      <c r="T6" s="98"/>
+      <c r="U6" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="V6" s="105"/>
-      <c r="W6" s="117" t="s">
+      <c r="V6" s="98"/>
+      <c r="W6" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="X6" s="105"/>
+      <c r="X6" s="98"/>
       <c r="Y6" s="10"/>
       <c r="Z6" s="10"/>
       <c r="AA6" s="10"/>
@@ -2236,19 +2236,19 @@
       <c r="AL8" s="20"/>
     </row>
     <row r="9" spans="1:38" ht="12" customHeight="1">
-      <c r="A9" s="94">
+      <c r="A9" s="93">
         <v>1</v>
       </c>
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="92">
+      <c r="C9" s="95">
         <v>2</v>
       </c>
-      <c r="D9" s="92" t="s">
+      <c r="D9" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="92"/>
+      <c r="E9" s="95"/>
       <c r="F9" s="21" t="s">
         <v>13</v>
       </c>
@@ -2286,16 +2286,16 @@
       <c r="AL9" s="27"/>
     </row>
     <row r="10" spans="1:38" ht="12" customHeight="1">
-      <c r="A10" s="93"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
+      <c r="A10" s="94"/>
+      <c r="B10" s="94"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="94"/>
       <c r="F10" s="28" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="29"/>
-      <c r="H10" s="118"/>
+      <c r="H10" s="92"/>
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
       <c r="K10" s="30"/>
@@ -2328,19 +2328,19 @@
       <c r="AL10" s="32"/>
     </row>
     <row r="11" spans="1:38" ht="12" customHeight="1">
-      <c r="A11" s="94">
+      <c r="A11" s="93">
         <v>2</v>
       </c>
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="92">
+      <c r="C11" s="95">
         <v>2</v>
       </c>
-      <c r="D11" s="92" t="s">
+      <c r="D11" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="92"/>
+      <c r="E11" s="95"/>
       <c r="F11" s="33" t="s">
         <v>13</v>
       </c>
@@ -2378,11 +2378,11 @@
       <c r="AL11" s="10"/>
     </row>
     <row r="12" spans="1:38" ht="12" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
       <c r="F12" s="37" t="s">
         <v>14</v>
       </c>
@@ -2420,19 +2420,19 @@
       <c r="AL12" s="41"/>
     </row>
     <row r="13" spans="1:38" ht="12" customHeight="1">
-      <c r="A13" s="94">
+      <c r="A13" s="93">
         <v>3</v>
       </c>
-      <c r="B13" s="92" t="s">
+      <c r="B13" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="92">
+      <c r="C13" s="95">
         <v>1</v>
       </c>
-      <c r="D13" s="92" t="s">
+      <c r="D13" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="92"/>
+      <c r="E13" s="95"/>
       <c r="F13" s="21" t="s">
         <v>13</v>
       </c>
@@ -2470,11 +2470,11 @@
       <c r="AL13" s="27"/>
     </row>
     <row r="14" spans="1:38" ht="12" customHeight="1">
-      <c r="A14" s="93"/>
-      <c r="B14" s="93"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="93"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
+      <c r="E14" s="94"/>
       <c r="F14" s="42" t="s">
         <v>14</v>
       </c>
@@ -2512,13 +2512,13 @@
       <c r="AL14" s="32"/>
     </row>
     <row r="15" spans="1:38" ht="12" customHeight="1">
-      <c r="A15" s="94">
+      <c r="A15" s="93">
         <v>4</v>
       </c>
-      <c r="B15" s="92"/>
-      <c r="C15" s="92"/>
-      <c r="D15" s="92"/>
-      <c r="E15" s="92"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
       <c r="F15" s="33" t="s">
         <v>13</v>
       </c>
@@ -2556,11 +2556,11 @@
       <c r="AL15" s="10"/>
     </row>
     <row r="16" spans="1:38" ht="12" customHeight="1">
-      <c r="A16" s="93"/>
-      <c r="B16" s="93"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="94"/>
+      <c r="C16" s="94"/>
+      <c r="D16" s="94"/>
+      <c r="E16" s="94"/>
       <c r="F16" s="37" t="s">
         <v>14</v>
       </c>
@@ -2598,17 +2598,19 @@
       <c r="AL16" s="41"/>
     </row>
     <row r="17" spans="1:38" ht="12" customHeight="1">
-      <c r="A17" s="94">
+      <c r="A17" s="93">
         <v>7</v>
       </c>
-      <c r="B17" s="92" t="s">
+      <c r="B17" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="92">
+      <c r="C17" s="95">
         <v>1</v>
       </c>
-      <c r="D17" s="92"/>
-      <c r="E17" s="92"/>
+      <c r="D17" s="95" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="95"/>
       <c r="F17" s="54" t="s">
         <v>13</v>
       </c>
@@ -2646,11 +2648,11 @@
       <c r="AL17" s="69"/>
     </row>
     <row r="18" spans="1:38" ht="12" customHeight="1">
-      <c r="A18" s="93"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="96"/>
       <c r="F18" s="37" t="s">
         <v>14</v>
       </c>
@@ -2688,13 +2690,13 @@
       <c r="AL18" s="12"/>
     </row>
     <row r="19" spans="1:38" ht="12" customHeight="1">
-      <c r="A19" s="94">
+      <c r="A19" s="93">
         <v>8</v>
       </c>
-      <c r="B19" s="92"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="92"/>
-      <c r="E19" s="92"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
       <c r="F19" s="54" t="s">
         <v>13</v>
       </c>
@@ -2732,11 +2734,11 @@
       <c r="AL19" s="69"/>
     </row>
     <row r="20" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A20" s="93"/>
-      <c r="B20" s="95"/>
-      <c r="C20" s="95"/>
-      <c r="D20" s="95"/>
-      <c r="E20" s="95"/>
+      <c r="A20" s="94"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="96"/>
       <c r="F20" s="37" t="s">
         <v>14</v>
       </c>
@@ -2774,17 +2776,19 @@
       <c r="AL20" s="12"/>
     </row>
     <row r="21" spans="1:38" ht="12" customHeight="1">
-      <c r="A21" s="94">
+      <c r="A21" s="93">
         <v>9</v>
       </c>
-      <c r="B21" s="92" t="s">
+      <c r="B21" s="95" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="92">
+      <c r="C21" s="95">
         <v>2</v>
       </c>
-      <c r="D21" s="92"/>
-      <c r="E21" s="92"/>
+      <c r="D21" s="95" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="95"/>
       <c r="F21" s="21" t="s">
         <v>13</v>
       </c>
@@ -2822,11 +2826,11 @@
       <c r="AL21" s="27"/>
     </row>
     <row r="22" spans="1:38" ht="12" customHeight="1">
-      <c r="A22" s="93"/>
-      <c r="B22" s="93"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
+      <c r="A22" s="94"/>
+      <c r="B22" s="94"/>
+      <c r="C22" s="94"/>
+      <c r="D22" s="94"/>
+      <c r="E22" s="94"/>
       <c r="F22" s="42" t="s">
         <v>14</v>
       </c>
@@ -2864,17 +2868,19 @@
       <c r="AL22" s="46"/>
     </row>
     <row r="23" spans="1:38" ht="12" customHeight="1">
-      <c r="A23" s="94">
+      <c r="A23" s="93">
         <v>10</v>
       </c>
-      <c r="B23" s="92" t="s">
+      <c r="B23" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="92">
+      <c r="C23" s="95">
         <v>2</v>
       </c>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
+      <c r="D23" s="95" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="95"/>
       <c r="F23" s="33" t="s">
         <v>13</v>
       </c>
@@ -2912,11 +2918,11 @@
       <c r="AL23" s="10"/>
     </row>
     <row r="24" spans="1:38" ht="12" customHeight="1">
-      <c r="A24" s="93"/>
-      <c r="B24" s="95"/>
-      <c r="C24" s="95"/>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
+      <c r="A24" s="94"/>
+      <c r="B24" s="96"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="96"/>
+      <c r="E24" s="96"/>
       <c r="F24" s="37" t="s">
         <v>14</v>
       </c>
@@ -2954,17 +2960,19 @@
       <c r="AL24" s="12"/>
     </row>
     <row r="25" spans="1:38" ht="12" customHeight="1">
-      <c r="A25" s="94">
+      <c r="A25" s="93">
         <v>11</v>
       </c>
-      <c r="B25" s="92" t="s">
+      <c r="B25" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="92">
+      <c r="C25" s="95">
         <v>1</v>
       </c>
-      <c r="D25" s="92"/>
-      <c r="E25" s="92"/>
+      <c r="D25" s="95" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="95"/>
       <c r="F25" s="54" t="s">
         <v>13</v>
       </c>
@@ -3002,11 +3010,11 @@
       <c r="AL25" s="69"/>
     </row>
     <row r="26" spans="1:38" ht="12" customHeight="1">
-      <c r="A26" s="93"/>
-      <c r="B26" s="95"/>
-      <c r="C26" s="95"/>
-      <c r="D26" s="95"/>
-      <c r="E26" s="95"/>
+      <c r="A26" s="94"/>
+      <c r="B26" s="96"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
       <c r="F26" s="37" t="s">
         <v>14</v>
       </c>
@@ -3044,13 +3052,13 @@
       <c r="AL26" s="12"/>
     </row>
     <row r="27" spans="1:38" ht="12" customHeight="1">
-      <c r="A27" s="94">
+      <c r="A27" s="93">
         <v>12</v>
       </c>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="92"/>
-      <c r="E27" s="92"/>
+      <c r="B27" s="95"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="95"/>
       <c r="F27" s="54" t="s">
         <v>13</v>
       </c>
@@ -3088,11 +3096,11 @@
       <c r="AL27" s="69"/>
     </row>
     <row r="28" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A28" s="93"/>
-      <c r="B28" s="95"/>
-      <c r="C28" s="95"/>
-      <c r="D28" s="95"/>
-      <c r="E28" s="95"/>
+      <c r="A28" s="94"/>
+      <c r="B28" s="96"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="96"/>
       <c r="F28" s="37" t="s">
         <v>14</v>
       </c>
@@ -3130,15 +3138,15 @@
       <c r="AL28" s="12"/>
     </row>
     <row r="29" spans="1:38" ht="12" customHeight="1">
-      <c r="A29" s="94">
+      <c r="A29" s="93">
         <v>12</v>
       </c>
-      <c r="B29" s="92" t="s">
+      <c r="B29" s="95" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="92"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92"/>
+      <c r="C29" s="95"/>
+      <c r="D29" s="95"/>
+      <c r="E29" s="95"/>
       <c r="F29" s="54" t="s">
         <v>13</v>
       </c>
@@ -3176,11 +3184,11 @@
       <c r="AL29" s="69"/>
     </row>
     <row r="30" spans="1:38" ht="13.5" customHeight="1">
-      <c r="A30" s="93"/>
-      <c r="B30" s="95"/>
-      <c r="C30" s="95"/>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
+      <c r="A30" s="94"/>
+      <c r="B30" s="96"/>
+      <c r="C30" s="96"/>
+      <c r="D30" s="96"/>
+      <c r="E30" s="96"/>
       <c r="F30" s="37" t="s">
         <v>14</v>
       </c>
@@ -3260,17 +3268,17 @@
       <c r="AL31" s="20"/>
     </row>
     <row r="32" spans="1:38" ht="12" customHeight="1">
-      <c r="A32" s="94">
+      <c r="A32" s="93">
         <v>1</v>
       </c>
-      <c r="B32" s="92" t="s">
+      <c r="B32" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="92">
+      <c r="C32" s="95">
         <v>0.5</v>
       </c>
-      <c r="D32" s="92"/>
-      <c r="E32" s="92"/>
+      <c r="D32" s="95"/>
+      <c r="E32" s="95"/>
       <c r="F32" s="21" t="s">
         <v>13</v>
       </c>
@@ -3307,11 +3315,11 @@
       <c r="AL32" s="27"/>
     </row>
     <row r="33" spans="1:38" ht="12" customHeight="1">
-      <c r="A33" s="93"/>
-      <c r="B33" s="95"/>
-      <c r="C33" s="93"/>
-      <c r="D33" s="93"/>
-      <c r="E33" s="93"/>
+      <c r="A33" s="94"/>
+      <c r="B33" s="96"/>
+      <c r="C33" s="94"/>
+      <c r="D33" s="94"/>
+      <c r="E33" s="94"/>
       <c r="F33" s="28" t="s">
         <v>14</v>
       </c>
@@ -3349,17 +3357,17 @@
       <c r="AL33" s="32"/>
     </row>
     <row r="34" spans="1:38" ht="12" customHeight="1">
-      <c r="A34" s="94">
+      <c r="A34" s="93">
         <v>2</v>
       </c>
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="92">
+      <c r="C34" s="95">
         <v>4</v>
       </c>
-      <c r="D34" s="92"/>
-      <c r="E34" s="92"/>
+      <c r="D34" s="95"/>
+      <c r="E34" s="95"/>
       <c r="F34" s="33" t="s">
         <v>13</v>
       </c>
@@ -3397,11 +3405,11 @@
       <c r="AL34" s="10"/>
     </row>
     <row r="35" spans="1:38" ht="12" customHeight="1">
-      <c r="A35" s="93"/>
-      <c r="B35" s="95"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="93"/>
-      <c r="E35" s="93"/>
+      <c r="A35" s="94"/>
+      <c r="B35" s="96"/>
+      <c r="C35" s="94"/>
+      <c r="D35" s="94"/>
+      <c r="E35" s="94"/>
       <c r="F35" s="37" t="s">
         <v>14</v>
       </c>
@@ -3439,17 +3447,17 @@
       <c r="AL35" s="41"/>
     </row>
     <row r="36" spans="1:38" ht="12" customHeight="1">
-      <c r="A36" s="94">
+      <c r="A36" s="93">
         <v>3</v>
       </c>
-      <c r="B36" s="92" t="s">
+      <c r="B36" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="C36" s="92">
+      <c r="C36" s="95">
         <v>4</v>
       </c>
-      <c r="D36" s="92"/>
-      <c r="E36" s="92"/>
+      <c r="D36" s="95"/>
+      <c r="E36" s="95"/>
       <c r="F36" s="21" t="s">
         <v>13</v>
       </c>
@@ -3487,11 +3495,11 @@
       <c r="AL36" s="27"/>
     </row>
     <row r="37" spans="1:38" ht="12" customHeight="1">
-      <c r="A37" s="93"/>
-      <c r="B37" s="95"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="93"/>
-      <c r="E37" s="93"/>
+      <c r="A37" s="94"/>
+      <c r="B37" s="96"/>
+      <c r="C37" s="94"/>
+      <c r="D37" s="94"/>
+      <c r="E37" s="94"/>
       <c r="F37" s="42" t="s">
         <v>14</v>
       </c>
@@ -3528,13 +3536,13 @@
       <c r="AL37" s="32"/>
     </row>
     <row r="38" spans="1:38" ht="12" customHeight="1">
-      <c r="A38" s="94">
+      <c r="A38" s="93">
         <v>4</v>
       </c>
-      <c r="B38" s="92"/>
-      <c r="C38" s="92"/>
-      <c r="D38" s="92"/>
-      <c r="E38" s="92"/>
+      <c r="B38" s="95"/>
+      <c r="C38" s="95"/>
+      <c r="D38" s="95"/>
+      <c r="E38" s="95"/>
       <c r="F38" s="33" t="s">
         <v>13</v>
       </c>
@@ -3572,11 +3580,11 @@
       <c r="AL38" s="10"/>
     </row>
     <row r="39" spans="1:38" ht="12" customHeight="1">
-      <c r="A39" s="93"/>
-      <c r="B39" s="95"/>
-      <c r="C39" s="95"/>
-      <c r="D39" s="95"/>
-      <c r="E39" s="95"/>
+      <c r="A39" s="94"/>
+      <c r="B39" s="96"/>
+      <c r="C39" s="96"/>
+      <c r="D39" s="96"/>
+      <c r="E39" s="96"/>
       <c r="F39" s="37" t="s">
         <v>14</v>
       </c>
@@ -3614,17 +3622,17 @@
       <c r="AL39" s="41"/>
     </row>
     <row r="40" spans="1:38" ht="12" customHeight="1">
-      <c r="A40" s="94">
+      <c r="A40" s="93">
         <v>5</v>
       </c>
-      <c r="B40" s="92" t="s">
+      <c r="B40" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="92">
+      <c r="C40" s="95">
         <v>0.5</v>
       </c>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
       <c r="F40" s="79" t="s">
         <v>13</v>
       </c>
@@ -3662,11 +3670,11 @@
       <c r="AL40" s="84"/>
     </row>
     <row r="41" spans="1:38" ht="12" customHeight="1">
-      <c r="A41" s="93"/>
-      <c r="B41" s="95"/>
-      <c r="C41" s="95"/>
-      <c r="D41" s="95"/>
-      <c r="E41" s="95"/>
+      <c r="A41" s="94"/>
+      <c r="B41" s="96"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
       <c r="F41" s="37" t="s">
         <v>14</v>
       </c>
@@ -3704,13 +3712,13 @@
       <c r="AL41" s="41"/>
     </row>
     <row r="42" spans="1:38" ht="12" customHeight="1">
-      <c r="A42" s="94">
+      <c r="A42" s="93">
         <v>6</v>
       </c>
-      <c r="B42" s="92"/>
-      <c r="C42" s="92"/>
-      <c r="D42" s="92"/>
-      <c r="E42" s="92"/>
+      <c r="B42" s="95"/>
+      <c r="C42" s="95"/>
+      <c r="D42" s="95"/>
+      <c r="E42" s="95"/>
       <c r="F42" s="21" t="s">
         <v>13</v>
       </c>
@@ -3747,11 +3755,11 @@
       <c r="AL42" s="27"/>
     </row>
     <row r="43" spans="1:38" ht="12" customHeight="1">
-      <c r="A43" s="93"/>
-      <c r="B43" s="95"/>
-      <c r="C43" s="93"/>
-      <c r="D43" s="93"/>
-      <c r="E43" s="93"/>
+      <c r="A43" s="94"/>
+      <c r="B43" s="96"/>
+      <c r="C43" s="94"/>
+      <c r="D43" s="94"/>
+      <c r="E43" s="94"/>
       <c r="F43" s="42" t="s">
         <v>14</v>
       </c>
@@ -3789,17 +3797,17 @@
       <c r="AL43" s="46"/>
     </row>
     <row r="44" spans="1:38" ht="12" customHeight="1">
-      <c r="A44" s="94">
+      <c r="A44" s="93">
         <v>7</v>
       </c>
-      <c r="B44" s="92" t="s">
+      <c r="B44" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="C44" s="92">
+      <c r="C44" s="95">
         <v>0.5</v>
       </c>
-      <c r="D44" s="92"/>
-      <c r="E44" s="92"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
       <c r="F44" s="21" t="s">
         <v>13</v>
       </c>
@@ -3837,11 +3845,11 @@
       <c r="AL44" s="27"/>
     </row>
     <row r="45" spans="1:38" ht="12" customHeight="1">
-      <c r="A45" s="93"/>
-      <c r="B45" s="95"/>
-      <c r="C45" s="93"/>
-      <c r="D45" s="93"/>
-      <c r="E45" s="93"/>
+      <c r="A45" s="94"/>
+      <c r="B45" s="96"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
       <c r="F45" s="42" t="s">
         <v>14</v>
       </c>
@@ -3879,17 +3887,17 @@
       <c r="AL45" s="46"/>
     </row>
     <row r="46" spans="1:38" ht="12" customHeight="1">
-      <c r="A46" s="94">
+      <c r="A46" s="93">
         <v>8</v>
       </c>
-      <c r="B46" s="92" t="s">
+      <c r="B46" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="C46" s="92">
+      <c r="C46" s="95">
         <v>4</v>
       </c>
-      <c r="D46" s="92"/>
-      <c r="E46" s="92"/>
+      <c r="D46" s="95"/>
+      <c r="E46" s="95"/>
       <c r="F46" s="21" t="s">
         <v>13</v>
       </c>
@@ -3926,11 +3934,11 @@
       <c r="AL46" s="27"/>
     </row>
     <row r="47" spans="1:38" ht="12" customHeight="1">
-      <c r="A47" s="93"/>
-      <c r="B47" s="95"/>
-      <c r="C47" s="93"/>
-      <c r="D47" s="93"/>
-      <c r="E47" s="93"/>
+      <c r="A47" s="94"/>
+      <c r="B47" s="96"/>
+      <c r="C47" s="94"/>
+      <c r="D47" s="94"/>
+      <c r="E47" s="94"/>
       <c r="F47" s="42" t="s">
         <v>14</v>
       </c>
@@ -3968,13 +3976,13 @@
       <c r="AL47" s="46"/>
     </row>
     <row r="48" spans="1:38" ht="12" customHeight="1">
-      <c r="A48" s="94">
+      <c r="A48" s="93">
         <v>9</v>
       </c>
-      <c r="B48" s="92"/>
-      <c r="C48" s="92"/>
-      <c r="D48" s="92"/>
-      <c r="E48" s="92"/>
+      <c r="B48" s="95"/>
+      <c r="C48" s="95"/>
+      <c r="D48" s="95"/>
+      <c r="E48" s="95"/>
       <c r="F48" s="21" t="s">
         <v>13</v>
       </c>
@@ -4012,11 +4020,11 @@
       <c r="AL48" s="27"/>
     </row>
     <row r="49" spans="1:38" ht="12" customHeight="1">
-      <c r="A49" s="93"/>
-      <c r="B49" s="95"/>
-      <c r="C49" s="93"/>
-      <c r="D49" s="93"/>
-      <c r="E49" s="93"/>
+      <c r="A49" s="94"/>
+      <c r="B49" s="96"/>
+      <c r="C49" s="94"/>
+      <c r="D49" s="94"/>
+      <c r="E49" s="94"/>
       <c r="F49" s="42" t="s">
         <v>14</v>
       </c>
@@ -4054,15 +4062,15 @@
       <c r="AL49" s="46"/>
     </row>
     <row r="50" spans="1:38" ht="11.25" customHeight="1">
-      <c r="A50" s="94">
+      <c r="A50" s="93">
         <v>10</v>
       </c>
-      <c r="B50" s="92" t="s">
+      <c r="B50" s="95" t="s">
         <v>35</v>
       </c>
-      <c r="C50" s="92"/>
-      <c r="D50" s="92"/>
-      <c r="E50" s="92"/>
+      <c r="C50" s="95"/>
+      <c r="D50" s="95"/>
+      <c r="E50" s="95"/>
       <c r="F50" s="33" t="s">
         <v>13</v>
       </c>
@@ -4100,11 +4108,11 @@
       <c r="AL50" s="10"/>
     </row>
     <row r="51" spans="1:38" ht="12" customHeight="1">
-      <c r="A51" s="93"/>
-      <c r="B51" s="95"/>
-      <c r="C51" s="93"/>
-      <c r="D51" s="93"/>
-      <c r="E51" s="93"/>
+      <c r="A51" s="94"/>
+      <c r="B51" s="96"/>
+      <c r="C51" s="94"/>
+      <c r="D51" s="94"/>
+      <c r="E51" s="94"/>
       <c r="F51" s="37" t="s">
         <v>14</v>
       </c>
@@ -4182,15 +4190,15 @@
       <c r="AL52" s="20"/>
     </row>
     <row r="53" spans="1:38" ht="12" customHeight="1">
-      <c r="A53" s="94">
+      <c r="A53" s="93">
         <v>1</v>
       </c>
-      <c r="B53" s="92" t="s">
+      <c r="B53" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C53" s="92"/>
-      <c r="D53" s="92"/>
-      <c r="E53" s="92"/>
+      <c r="C53" s="95"/>
+      <c r="D53" s="95"/>
+      <c r="E53" s="95"/>
       <c r="F53" s="21" t="s">
         <v>13</v>
       </c>
@@ -4228,11 +4236,11 @@
       <c r="AL53" s="27"/>
     </row>
     <row r="54" spans="1:38" ht="12" customHeight="1">
-      <c r="A54" s="93"/>
-      <c r="B54" s="93"/>
-      <c r="C54" s="93"/>
-      <c r="D54" s="93"/>
-      <c r="E54" s="93"/>
+      <c r="A54" s="94"/>
+      <c r="B54" s="94"/>
+      <c r="C54" s="94"/>
+      <c r="D54" s="94"/>
+      <c r="E54" s="94"/>
       <c r="F54" s="28" t="s">
         <v>14</v>
       </c>
@@ -4270,15 +4278,15 @@
       <c r="AL54" s="32"/>
     </row>
     <row r="55" spans="1:38" ht="12" customHeight="1">
-      <c r="A55" s="94">
+      <c r="A55" s="93">
         <v>2</v>
       </c>
-      <c r="B55" s="92" t="s">
+      <c r="B55" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="C55" s="92"/>
-      <c r="D55" s="92"/>
-      <c r="E55" s="92"/>
+      <c r="C55" s="95"/>
+      <c r="D55" s="95"/>
+      <c r="E55" s="95"/>
       <c r="F55" s="33" t="s">
         <v>13</v>
       </c>
@@ -4316,11 +4324,11 @@
       <c r="AL55" s="10"/>
     </row>
     <row r="56" spans="1:38" ht="12" customHeight="1">
-      <c r="A56" s="93"/>
-      <c r="B56" s="93"/>
-      <c r="C56" s="93"/>
-      <c r="D56" s="93"/>
-      <c r="E56" s="93"/>
+      <c r="A56" s="94"/>
+      <c r="B56" s="94"/>
+      <c r="C56" s="94"/>
+      <c r="D56" s="94"/>
+      <c r="E56" s="94"/>
       <c r="F56" s="37" t="s">
         <v>14</v>
       </c>
@@ -4358,15 +4366,15 @@
       <c r="AL56" s="41"/>
     </row>
     <row r="57" spans="1:38" ht="12" customHeight="1">
-      <c r="A57" s="94">
+      <c r="A57" s="93">
         <v>3</v>
       </c>
-      <c r="B57" s="92" t="s">
+      <c r="B57" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="C57" s="92"/>
-      <c r="D57" s="92"/>
-      <c r="E57" s="92"/>
+      <c r="C57" s="95"/>
+      <c r="D57" s="95"/>
+      <c r="E57" s="95"/>
       <c r="F57" s="21" t="s">
         <v>13</v>
       </c>
@@ -4404,11 +4412,11 @@
       <c r="AL57" s="27"/>
     </row>
     <row r="58" spans="1:38" ht="12" customHeight="1">
-      <c r="A58" s="93"/>
-      <c r="B58" s="93"/>
-      <c r="C58" s="93"/>
-      <c r="D58" s="93"/>
-      <c r="E58" s="93"/>
+      <c r="A58" s="94"/>
+      <c r="B58" s="94"/>
+      <c r="C58" s="94"/>
+      <c r="D58" s="94"/>
+      <c r="E58" s="94"/>
       <c r="F58" s="42" t="s">
         <v>14</v>
       </c>
@@ -4446,15 +4454,15 @@
       <c r="AL58" s="32"/>
     </row>
     <row r="59" spans="1:38" ht="12" customHeight="1">
-      <c r="A59" s="94">
+      <c r="A59" s="93">
         <v>4</v>
       </c>
-      <c r="B59" s="92" t="s">
+      <c r="B59" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="C59" s="92"/>
-      <c r="D59" s="92"/>
-      <c r="E59" s="92"/>
+      <c r="C59" s="95"/>
+      <c r="D59" s="95"/>
+      <c r="E59" s="95"/>
       <c r="F59" s="21" t="s">
         <v>13</v>
       </c>
@@ -4492,11 +4500,11 @@
       <c r="AL59" s="27"/>
     </row>
     <row r="60" spans="1:38" ht="12" customHeight="1">
-      <c r="A60" s="93"/>
-      <c r="B60" s="93"/>
-      <c r="C60" s="93"/>
-      <c r="D60" s="93"/>
-      <c r="E60" s="93"/>
+      <c r="A60" s="94"/>
+      <c r="B60" s="94"/>
+      <c r="C60" s="94"/>
+      <c r="D60" s="94"/>
+      <c r="E60" s="94"/>
       <c r="F60" s="42" t="s">
         <v>14</v>
       </c>
@@ -4534,13 +4542,13 @@
       <c r="AL60" s="46"/>
     </row>
     <row r="61" spans="1:38" ht="12" customHeight="1">
-      <c r="A61" s="94">
+      <c r="A61" s="93">
         <v>5</v>
       </c>
-      <c r="B61" s="92"/>
-      <c r="C61" s="92"/>
-      <c r="D61" s="92"/>
-      <c r="E61" s="92"/>
+      <c r="B61" s="95"/>
+      <c r="C61" s="95"/>
+      <c r="D61" s="95"/>
+      <c r="E61" s="95"/>
       <c r="F61" s="33" t="s">
         <v>13</v>
       </c>
@@ -4578,11 +4586,11 @@
       <c r="AL61" s="10"/>
     </row>
     <row r="62" spans="1:38" ht="12" customHeight="1">
-      <c r="A62" s="93"/>
-      <c r="B62" s="93"/>
-      <c r="C62" s="93"/>
-      <c r="D62" s="93"/>
-      <c r="E62" s="93"/>
+      <c r="A62" s="94"/>
+      <c r="B62" s="94"/>
+      <c r="C62" s="94"/>
+      <c r="D62" s="94"/>
+      <c r="E62" s="94"/>
       <c r="F62" s="37" t="s">
         <v>14</v>
       </c>
@@ -4662,13 +4670,13 @@
       <c r="AL63" s="20"/>
     </row>
     <row r="64" spans="1:38" ht="12" customHeight="1">
-      <c r="A64" s="94">
+      <c r="A64" s="93">
         <v>1</v>
       </c>
-      <c r="B64" s="92"/>
-      <c r="C64" s="92"/>
-      <c r="D64" s="92"/>
-      <c r="E64" s="92"/>
+      <c r="B64" s="95"/>
+      <c r="C64" s="95"/>
+      <c r="D64" s="95"/>
+      <c r="E64" s="95"/>
       <c r="F64" s="21" t="s">
         <v>13</v>
       </c>
@@ -4706,11 +4714,11 @@
       <c r="AL64" s="27"/>
     </row>
     <row r="65" spans="1:38" ht="12" customHeight="1">
-      <c r="A65" s="93"/>
-      <c r="B65" s="93"/>
-      <c r="C65" s="93"/>
-      <c r="D65" s="93"/>
-      <c r="E65" s="93"/>
+      <c r="A65" s="94"/>
+      <c r="B65" s="94"/>
+      <c r="C65" s="94"/>
+      <c r="D65" s="94"/>
+      <c r="E65" s="94"/>
       <c r="F65" s="28" t="s">
         <v>14</v>
       </c>
@@ -4748,13 +4756,13 @@
       <c r="AL65" s="32"/>
     </row>
     <row r="66" spans="1:38" ht="12" customHeight="1">
-      <c r="A66" s="94">
+      <c r="A66" s="93">
         <v>2</v>
       </c>
-      <c r="B66" s="92"/>
-      <c r="C66" s="92"/>
-      <c r="D66" s="92"/>
-      <c r="E66" s="92"/>
+      <c r="B66" s="95"/>
+      <c r="C66" s="95"/>
+      <c r="D66" s="95"/>
+      <c r="E66" s="95"/>
       <c r="F66" s="33" t="s">
         <v>13</v>
       </c>
@@ -4792,11 +4800,11 @@
       <c r="AL66" s="10"/>
     </row>
     <row r="67" spans="1:38" ht="12" customHeight="1">
-      <c r="A67" s="93"/>
-      <c r="B67" s="93"/>
-      <c r="C67" s="93"/>
-      <c r="D67" s="93"/>
-      <c r="E67" s="93"/>
+      <c r="A67" s="94"/>
+      <c r="B67" s="94"/>
+      <c r="C67" s="94"/>
+      <c r="D67" s="94"/>
+      <c r="E67" s="94"/>
       <c r="F67" s="37" t="s">
         <v>14</v>
       </c>
@@ -4834,13 +4842,13 @@
       <c r="AL67" s="41"/>
     </row>
     <row r="68" spans="1:38" ht="12" customHeight="1">
-      <c r="A68" s="94">
+      <c r="A68" s="93">
         <v>3</v>
       </c>
-      <c r="B68" s="92"/>
-      <c r="C68" s="92"/>
-      <c r="D68" s="92"/>
-      <c r="E68" s="92"/>
+      <c r="B68" s="95"/>
+      <c r="C68" s="95"/>
+      <c r="D68" s="95"/>
+      <c r="E68" s="95"/>
       <c r="F68" s="21" t="s">
         <v>13</v>
       </c>
@@ -4878,11 +4886,11 @@
       <c r="AL68" s="27"/>
     </row>
     <row r="69" spans="1:38" ht="12" customHeight="1">
-      <c r="A69" s="93"/>
-      <c r="B69" s="93"/>
-      <c r="C69" s="93"/>
-      <c r="D69" s="93"/>
-      <c r="E69" s="93"/>
+      <c r="A69" s="94"/>
+      <c r="B69" s="94"/>
+      <c r="C69" s="94"/>
+      <c r="D69" s="94"/>
+      <c r="E69" s="94"/>
       <c r="F69" s="42" t="s">
         <v>14</v>
       </c>
@@ -4920,13 +4928,13 @@
       <c r="AL69" s="32"/>
     </row>
     <row r="70" spans="1:38" ht="12" customHeight="1">
-      <c r="A70" s="94">
+      <c r="A70" s="93">
         <v>4</v>
       </c>
-      <c r="B70" s="92"/>
-      <c r="C70" s="92"/>
-      <c r="D70" s="92"/>
-      <c r="E70" s="92"/>
+      <c r="B70" s="95"/>
+      <c r="C70" s="95"/>
+      <c r="D70" s="95"/>
+      <c r="E70" s="95"/>
       <c r="F70" s="33" t="s">
         <v>13</v>
       </c>
@@ -4964,11 +4972,11 @@
       <c r="AL70" s="10"/>
     </row>
     <row r="71" spans="1:38" ht="12" customHeight="1">
-      <c r="A71" s="93"/>
-      <c r="B71" s="93"/>
-      <c r="C71" s="93"/>
-      <c r="D71" s="93"/>
-      <c r="E71" s="93"/>
+      <c r="A71" s="94"/>
+      <c r="B71" s="94"/>
+      <c r="C71" s="94"/>
+      <c r="D71" s="94"/>
+      <c r="E71" s="94"/>
       <c r="F71" s="37" t="s">
         <v>14</v>
       </c>
@@ -5006,13 +5014,13 @@
       <c r="AL71" s="41"/>
     </row>
     <row r="72" spans="1:38" ht="12" customHeight="1">
-      <c r="A72" s="94">
+      <c r="A72" s="93">
         <v>5</v>
       </c>
-      <c r="B72" s="92"/>
-      <c r="C72" s="92"/>
-      <c r="D72" s="92"/>
-      <c r="E72" s="92"/>
+      <c r="B72" s="95"/>
+      <c r="C72" s="95"/>
+      <c r="D72" s="95"/>
+      <c r="E72" s="95"/>
       <c r="F72" s="21" t="s">
         <v>13</v>
       </c>
@@ -5050,11 +5058,11 @@
       <c r="AL72" s="27"/>
     </row>
     <row r="73" spans="1:38" ht="12" customHeight="1">
-      <c r="A73" s="93"/>
-      <c r="B73" s="93"/>
-      <c r="C73" s="93"/>
-      <c r="D73" s="93"/>
-      <c r="E73" s="93"/>
+      <c r="A73" s="94"/>
+      <c r="B73" s="94"/>
+      <c r="C73" s="94"/>
+      <c r="D73" s="94"/>
+      <c r="E73" s="94"/>
       <c r="F73" s="42" t="s">
         <v>14</v>
       </c>
@@ -5092,13 +5100,13 @@
       <c r="AL73" s="46"/>
     </row>
     <row r="74" spans="1:38" ht="12" customHeight="1">
-      <c r="A74" s="94">
+      <c r="A74" s="93">
         <v>6</v>
       </c>
-      <c r="B74" s="92"/>
-      <c r="C74" s="92"/>
-      <c r="D74" s="92"/>
-      <c r="E74" s="92"/>
+      <c r="B74" s="95"/>
+      <c r="C74" s="95"/>
+      <c r="D74" s="95"/>
+      <c r="E74" s="95"/>
       <c r="F74" s="33" t="s">
         <v>13</v>
       </c>
@@ -5136,11 +5144,11 @@
       <c r="AL74" s="10"/>
     </row>
     <row r="75" spans="1:38" ht="12" customHeight="1">
-      <c r="A75" s="93"/>
-      <c r="B75" s="93"/>
-      <c r="C75" s="93"/>
-      <c r="D75" s="93"/>
-      <c r="E75" s="93"/>
+      <c r="A75" s="94"/>
+      <c r="B75" s="94"/>
+      <c r="C75" s="94"/>
+      <c r="D75" s="94"/>
+      <c r="E75" s="94"/>
       <c r="F75" s="37" t="s">
         <v>14</v>
       </c>
@@ -5218,13 +5226,13 @@
       <c r="AL76" s="20"/>
     </row>
     <row r="77" spans="1:38" ht="12" customHeight="1">
-      <c r="A77" s="94">
+      <c r="A77" s="93">
         <v>1</v>
       </c>
-      <c r="B77" s="92"/>
-      <c r="C77" s="92"/>
-      <c r="D77" s="92"/>
-      <c r="E77" s="92"/>
+      <c r="B77" s="95"/>
+      <c r="C77" s="95"/>
+      <c r="D77" s="95"/>
+      <c r="E77" s="95"/>
       <c r="F77" s="21" t="s">
         <v>13</v>
       </c>
@@ -5262,11 +5270,11 @@
       <c r="AL77" s="27"/>
     </row>
     <row r="78" spans="1:38" ht="12" customHeight="1">
-      <c r="A78" s="93"/>
-      <c r="B78" s="93"/>
-      <c r="C78" s="93"/>
-      <c r="D78" s="93"/>
-      <c r="E78" s="93"/>
+      <c r="A78" s="94"/>
+      <c r="B78" s="94"/>
+      <c r="C78" s="94"/>
+      <c r="D78" s="94"/>
+      <c r="E78" s="94"/>
       <c r="F78" s="28" t="s">
         <v>14</v>
       </c>
@@ -5304,13 +5312,13 @@
       <c r="AL78" s="32"/>
     </row>
     <row r="79" spans="1:38" ht="12" customHeight="1">
-      <c r="A79" s="94">
+      <c r="A79" s="93">
         <v>2</v>
       </c>
-      <c r="B79" s="92"/>
-      <c r="C79" s="92"/>
-      <c r="D79" s="92"/>
-      <c r="E79" s="92"/>
+      <c r="B79" s="95"/>
+      <c r="C79" s="95"/>
+      <c r="D79" s="95"/>
+      <c r="E79" s="95"/>
       <c r="F79" s="33" t="s">
         <v>13</v>
       </c>
@@ -5348,11 +5356,11 @@
       <c r="AL79" s="10"/>
     </row>
     <row r="80" spans="1:38" ht="12" customHeight="1">
-      <c r="A80" s="93"/>
-      <c r="B80" s="93"/>
-      <c r="C80" s="93"/>
-      <c r="D80" s="93"/>
-      <c r="E80" s="93"/>
+      <c r="A80" s="94"/>
+      <c r="B80" s="94"/>
+      <c r="C80" s="94"/>
+      <c r="D80" s="94"/>
+      <c r="E80" s="94"/>
       <c r="F80" s="37" t="s">
         <v>14</v>
       </c>
@@ -5390,13 +5398,13 @@
       <c r="AL80" s="41"/>
     </row>
     <row r="81" spans="1:38" ht="12" customHeight="1">
-      <c r="A81" s="94">
+      <c r="A81" s="93">
         <v>3</v>
       </c>
-      <c r="B81" s="92"/>
-      <c r="C81" s="92"/>
-      <c r="D81" s="92"/>
-      <c r="E81" s="92"/>
+      <c r="B81" s="95"/>
+      <c r="C81" s="95"/>
+      <c r="D81" s="95"/>
+      <c r="E81" s="95"/>
       <c r="F81" s="21" t="s">
         <v>13</v>
       </c>
@@ -5434,11 +5442,11 @@
       <c r="AL81" s="27"/>
     </row>
     <row r="82" spans="1:38" ht="12" customHeight="1">
-      <c r="A82" s="93"/>
-      <c r="B82" s="93"/>
-      <c r="C82" s="93"/>
-      <c r="D82" s="93"/>
-      <c r="E82" s="93"/>
+      <c r="A82" s="94"/>
+      <c r="B82" s="94"/>
+      <c r="C82" s="94"/>
+      <c r="D82" s="94"/>
+      <c r="E82" s="94"/>
       <c r="F82" s="42" t="s">
         <v>14</v>
       </c>
@@ -5476,13 +5484,13 @@
       <c r="AL82" s="32"/>
     </row>
     <row r="83" spans="1:38" ht="12" customHeight="1">
-      <c r="A83" s="94">
+      <c r="A83" s="93">
         <v>4</v>
       </c>
-      <c r="B83" s="92"/>
-      <c r="C83" s="92"/>
-      <c r="D83" s="92"/>
-      <c r="E83" s="92"/>
+      <c r="B83" s="95"/>
+      <c r="C83" s="95"/>
+      <c r="D83" s="95"/>
+      <c r="E83" s="95"/>
       <c r="F83" s="33" t="s">
         <v>13</v>
       </c>
@@ -5520,11 +5528,11 @@
       <c r="AL83" s="10"/>
     </row>
     <row r="84" spans="1:38" ht="12" customHeight="1">
-      <c r="A84" s="93"/>
-      <c r="B84" s="93"/>
-      <c r="C84" s="93"/>
-      <c r="D84" s="93"/>
-      <c r="E84" s="93"/>
+      <c r="A84" s="94"/>
+      <c r="B84" s="94"/>
+      <c r="C84" s="94"/>
+      <c r="D84" s="94"/>
+      <c r="E84" s="94"/>
       <c r="F84" s="42" t="s">
         <v>14</v>
       </c>
@@ -42203,6 +42211,187 @@
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:AL4"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="E77:E78"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="A59:A60"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="B42:B43"/>
     <mergeCell ref="C42:C43"/>
@@ -42227,187 +42416,6 @@
     <mergeCell ref="B46:B47"/>
     <mergeCell ref="C46:C47"/>
     <mergeCell ref="D46:D47"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="E77:E78"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="E79:E80"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:AL4"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <dataValidations count="1">
